--- a/output_phyto/phyto_Intermediate_mejia_2017.xlsx
+++ b/output_phyto/phyto_Intermediate_mejia_2017.xlsx
@@ -1454,13 +1454,13 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_Mejia_2017_1</t>
+    <t xml:space="preserve">138-846B-4H-1,103-105</t>
   </si>
   <si>
     <t xml:space="preserve">10.1016/j.epsl.2017.08.034</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/phytoplankton_mejia_2017.xlsx</t>
+    <t xml:space="preserve">phytoplankton_mejia_2017_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>
@@ -1475,28 +1475,28 @@
     <t xml:space="preserve">pennate_diatom_frustule_bound_OM</t>
   </si>
   <si>
-    <t xml:space="preserve">alkenone unsaturation</t>
+    <t xml:space="preserve">published Uk37 temperature</t>
   </si>
   <si>
     <t xml:space="preserve">Several pCO2 estimates are provided, and absolute values are dependent on the choice of b or assumptions about HCO3 uptake. Because this site is in an upwelling region (EEP), we do not select a pCO2 history, and instead report only the geochemical data.</t>
   </si>
   <si>
-    <t xml:space="preserve">phytoplankton_Mejia_2017_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Mejia_2017_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Mejia_2017_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Mejia_2017_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Mejia_2017_6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">phytoplankton_Mejia_2017_7</t>
+    <t xml:space="preserve">138-846B-15H-4,103-105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-846B-22H-5,103-105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-846B-29X-1,103-105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-846B-31X-1,79-81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-846B-34X-2,125-127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">138-846B-38X-1,98-100</t>
   </si>
 </sst>
 </file>
@@ -1504,7 +1504,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1570,12 +1570,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1689,7 +1683,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1788,7 +1782,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2514,7 +2507,7 @@
       <c r="B5" t="s">
         <v>271</v>
       </c>
-      <c r="C5" s="34" t="s">
+      <c r="C5" t="s">
         <v>272</v>
       </c>
       <c r="D5" t="s">
@@ -2532,8 +2525,8 @@
       <c r="H5" t="n">
         <v>0.82</v>
       </c>
-      <c r="I5" t="e">
-        <v>#N/A</v>
+      <c r="I5" t="n">
+        <v>0.004</v>
       </c>
       <c r="J5" t="e">
         <v>#N/A</v>
@@ -2551,7 +2544,7 @@
         <v>-20.49</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P5" t="e">
         <v>#N/A</v>
@@ -2562,8 +2555,8 @@
       <c r="R5" s="11" t="n">
         <v>22.62</v>
       </c>
-      <c r="S5" t="e">
-        <v>#N/A</v>
+      <c r="S5" t="n">
+        <v>3</v>
       </c>
       <c r="T5" t="e">
         <v>#N/A</v>
@@ -2624,7 +2617,7 @@
       <c r="B6" t="s">
         <v>271</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" t="s">
         <v>272</v>
       </c>
       <c r="D6" t="s">
@@ -2642,8 +2635,8 @@
       <c r="H6" t="n">
         <v>3.99</v>
       </c>
-      <c r="I6" t="e">
-        <v>#N/A</v>
+      <c r="I6" t="n">
+        <v>0.015</v>
       </c>
       <c r="J6" t="e">
         <v>#N/A</v>
@@ -2661,7 +2654,7 @@
         <v>-20.02</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P6" t="e">
         <v>#N/A</v>
@@ -2672,8 +2665,8 @@
       <c r="R6" s="11" t="n">
         <v>26.02</v>
       </c>
-      <c r="S6" t="e">
-        <v>#N/A</v>
+      <c r="S6" t="n">
+        <v>3</v>
       </c>
       <c r="T6" t="e">
         <v>#N/A</v>
@@ -2734,7 +2727,7 @@
       <c r="B7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" t="s">
         <v>272</v>
       </c>
       <c r="D7" t="s">
@@ -2752,8 +2745,8 @@
       <c r="H7" t="n">
         <v>5.81</v>
       </c>
-      <c r="I7" t="e">
-        <v>#N/A</v>
+      <c r="I7" t="n">
+        <v>0.0307800911161256</v>
       </c>
       <c r="J7" t="e">
         <v>#N/A</v>
@@ -2771,7 +2764,7 @@
         <v>-21.58</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P7" t="e">
         <v>#N/A</v>
@@ -2782,8 +2775,8 @@
       <c r="R7" s="11" t="n">
         <v>26.57</v>
       </c>
-      <c r="S7" t="e">
-        <v>#N/A</v>
+      <c r="S7" t="n">
+        <v>3</v>
       </c>
       <c r="T7" t="e">
         <v>#N/A</v>
@@ -2844,7 +2837,7 @@
       <c r="B8" t="s">
         <v>271</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" t="s">
         <v>272</v>
       </c>
       <c r="D8" t="s">
@@ -2862,8 +2855,8 @@
       <c r="H8" t="n">
         <v>7.66</v>
       </c>
-      <c r="I8" t="e">
-        <v>#N/A</v>
+      <c r="I8" t="n">
+        <v>0.0400040362128825</v>
       </c>
       <c r="J8" t="e">
         <v>#N/A</v>
@@ -2881,7 +2874,7 @@
         <v>-22.57</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P8" t="e">
         <v>#N/A</v>
@@ -2892,8 +2885,8 @@
       <c r="R8" s="11" t="n">
         <v>28.33</v>
       </c>
-      <c r="S8" t="e">
-        <v>#N/A</v>
+      <c r="S8" t="n">
+        <v>3</v>
       </c>
       <c r="T8" t="e">
         <v>#N/A</v>
@@ -2954,7 +2947,7 @@
       <c r="B9" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" t="s">
         <v>272</v>
       </c>
       <c r="D9" t="s">
@@ -2972,8 +2965,8 @@
       <c r="H9" t="n">
         <v>8.86</v>
       </c>
-      <c r="I9" t="e">
-        <v>#N/A</v>
+      <c r="I9" t="n">
+        <v>0.0459234754282779</v>
       </c>
       <c r="J9" t="e">
         <v>#N/A</v>
@@ -2991,7 +2984,7 @@
         <v>-24.49</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P9" t="e">
         <v>#N/A</v>
@@ -3002,8 +2995,8 @@
       <c r="R9" s="11" t="n">
         <v>28.69</v>
       </c>
-      <c r="S9" t="e">
-        <v>#N/A</v>
+      <c r="S9" t="n">
+        <v>3</v>
       </c>
       <c r="T9" t="e">
         <v>#N/A</v>
@@ -3064,7 +3057,7 @@
       <c r="B10" t="s">
         <v>271</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" t="s">
         <v>272</v>
       </c>
       <c r="D10" t="s">
@@ -3082,8 +3075,8 @@
       <c r="H10" t="n">
         <v>10.85</v>
       </c>
-      <c r="I10" t="e">
-        <v>#N/A</v>
+      <c r="I10" t="n">
+        <v>0.0556509484216982</v>
       </c>
       <c r="J10" t="e">
         <v>#N/A</v>
@@ -3101,7 +3094,7 @@
         <v>-23.92</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P10" t="e">
         <v>#N/A</v>
@@ -3112,8 +3105,8 @@
       <c r="R10" s="11" t="n">
         <v>28.73</v>
       </c>
-      <c r="S10" t="e">
-        <v>#N/A</v>
+      <c r="S10" t="n">
+        <v>3</v>
       </c>
       <c r="T10" t="e">
         <v>#N/A</v>
@@ -3174,7 +3167,7 @@
       <c r="B11" t="s">
         <v>271</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" t="s">
         <v>272</v>
       </c>
       <c r="D11" t="s">
@@ -3192,8 +3185,8 @@
       <c r="H11" t="n">
         <v>12.89</v>
       </c>
-      <c r="I11" t="e">
-        <v>#N/A</v>
+      <c r="I11" t="n">
+        <v>0.0655269431710384</v>
       </c>
       <c r="J11" t="e">
         <v>#N/A</v>
@@ -3211,7 +3204,7 @@
         <v>-19.91</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8</v>
+        <v>0.565685424949238</v>
       </c>
       <c r="P11" t="e">
         <v>#N/A</v>
@@ -3222,8 +3215,8 @@
       <c r="R11" s="11" t="n">
         <v>28.74</v>
       </c>
-      <c r="S11" t="e">
-        <v>#N/A</v>
+      <c r="S11" t="n">
+        <v>3</v>
       </c>
       <c r="T11" t="e">
         <v>#N/A</v>
@@ -3667,15 +3660,6 @@
       <formula>#REF!="no"</formula>
     </cfRule>
   </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1h"/>
-    <hyperlink ref="C6" r:id="rId2h"/>
-    <hyperlink ref="C7" r:id="rId3h"/>
-    <hyperlink ref="C8" r:id="rId4h"/>
-    <hyperlink ref="C9" r:id="rId5h"/>
-    <hyperlink ref="C10" r:id="rId6h"/>
-    <hyperlink ref="C11" r:id="rId7h"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
